--- a/resources/data-imports/Quests/guide-quests.xlsx
+++ b/resources/data-imports/Quests/guide-quests.xlsx
@@ -377,10 +377,10 @@
     <t>&lt;p&gt;Let’s do what the Guide stated: Learn something about ourselves. Class Ranks.&lt;/p&gt;&lt;p&gt;&lt;a href="/information/class-ranks" target="_blank"&gt;Class Ranks&lt;/a&gt; allow you to switch classes and equip special abilities that can boost your character stats or even give you a special attack that will fire any time you attack an enemy allowing you to do even more damage.&lt;/p&gt;&lt;p&gt;Class Ranks come with, as mentioned, Specialties which as leveled make your character even stronger. To level them you just have to equip the ones you want and then go kill things using exploration – as manual leveling will take a very long time &lt;/p&gt;&lt;p&gt;and can be very grindy.&lt;/p&gt;&lt;p&gt;Class Ranks also come with masteries. As a character who has specific weapons equipped will level these masteries over time while killing creatures and gaining more bonuses to damage while using that weapon.&lt;/p&gt;&lt;p&gt;As mentioned before Characters can, at any time switch classes. You can level the rank of that class by killing creatures.&lt;/p&gt;&lt;p&gt;As you level the class itself and switch to other classes and level them, not only will you unlock the specialties you can equip (and thus mix and match) you will also eventually unlock other classes you can switch too that require you to level two or more classes.&lt;/p&gt;</t>
   </si>
   <si>
-    <t>&lt;ul&gt;&lt;li&gt;Click the Character Sheet Tab.&lt;/li&gt;&lt;li&gt;Click the Class Ranks Orange Button.&lt;/li&gt;&lt;li&gt;Look for your class in the list and click the name.&lt;/li&gt;&lt;li&gt;This will open another window, to exit back to the class list click the red circle with the minus in the top right. Clicking cancel or the X will close the modal.&lt;/li&gt;&lt;li&gt;Here you will see information about the class and the Class Masteries.&lt;/li&gt;&lt;li&gt;Click Manage Specialties.&lt;/li&gt;&lt;li&gt;Equip a specialty and boom done, now you just have to kill creatures.&lt;/li&gt;&lt;li&gt;The server messages will tell you when you gain levels in your Masteries and your Specialties as well as your Class Rank.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Now you just have to kill creatures till you meet the requirements.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;ul&gt;&lt;li&gt;Tap the Character Sheet tab.&lt;/li&gt;&lt;li&gt;Expand the Character Details Section.&lt;/li&gt;&lt;li&gt;Tap the Class Ranks orange button.&lt;/li&gt;&lt;li&gt;Look for your class in the list and tap the name.&lt;/li&gt;&lt;li&gt;This will open another window, to exit back to the class list tap the red circle with the minus in the top right. Tap cancel or the X will close the modal.&lt;/li&gt;&lt;li&gt;Here you will see information about the class and the Class Masteries.&lt;/li&gt;&lt;li&gt;Tap Manage Specialties.&lt;/li&gt;&lt;li&gt;Equip a specialty and boom done, now you just have to kill creatures.&lt;/li&gt;&lt;li&gt;The server messages will tell you when you gain levels in your Masteries and your Specialties as well as your Class Rank.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Now you just have to kill creatures till you meet the requirements.&lt;/p&gt;</t>
+    <t>&lt;ul&gt;&lt;li&gt;Click the Character Sheet Tab.&lt;/li&gt;&lt;li&gt;Click Show Additional Details.&lt;/li&gt;&lt;li&gt;On The Right hand side youll see a Class Ranks section.&lt;/li&gt;&lt;li&gt;Look for your class in the list and click the name.&lt;/li&gt;&lt;li&gt;This will open another window, to exit back to the class list click the red circle with the minus in the top right. Clicking cancel or the X will close the modal.&lt;/li&gt;&lt;li&gt;Here you will see information about the class and the Class Masteries.&lt;/li&gt;&lt;li&gt;Click Manage Specialties.&lt;/li&gt;&lt;li&gt;Equip a specialty and boom done, now you just have to kill creatures.&lt;/li&gt;&lt;li&gt;The server messages will tell you when you gain levels in your Masteries and your Specialties as well as your Class Rank.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Now you just have to kill creatures till you meet the requirements.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Tap the Character Sheet tab.&lt;/li&gt;&lt;li&gt;Expand the Character Details Section.&lt;/li&gt;&lt;li&gt;Click See additional Details.&lt;/li&gt;&lt;li&gt;Scroll down till you find the section.&lt;/li&gt;&lt;li&gt;Tap the Class Ranks orange button.&lt;/li&gt;&lt;li&gt;Look for your class in the list and tap the name.&lt;/li&gt;&lt;li&gt;This will open another window, to exit back to the class list tap the red circle with the minus in the top right. Tap cancel or the X will close the modal.&lt;/li&gt;&lt;li&gt;Here you will see information about the class and the Class Masteries.&lt;/li&gt;&lt;li&gt;Tap Manage Specialties.&lt;/li&gt;&lt;li&gt;Equip a specialty and boom done, now you just have to kill creatures.&lt;/li&gt;&lt;li&gt;The server messages will tell you when you gain levels in your Masteries and your Specialties as well as your Class Rank.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Now you just have to kill creatures till you meet the requirements.&lt;/p&gt;</t>
   </si>
   <si>
     <t>Farmers in the fields</t>

--- a/resources/data-imports/Quests/guide-quests.xlsx
+++ b/resources/data-imports/Quests/guide-quests.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="393">
   <si>
     <t>id</t>
   </si>
@@ -188,6 +188,42 @@
     <t>required_delve_pack_size</t>
   </si>
   <si>
+    <t>required_batch_crafting_type</t>
+  </si>
+  <si>
+    <t>required_batch_crafting_hours</t>
+  </si>
+  <si>
+    <t>required_item_1_source</t>
+  </si>
+  <si>
+    <t>required_item_1_name</t>
+  </si>
+  <si>
+    <t>required_item_1_type</t>
+  </si>
+  <si>
+    <t>required_item_1_amount</t>
+  </si>
+  <si>
+    <t>required_item_1_must_be_enchanted</t>
+  </si>
+  <si>
+    <t>required_item_2_source</t>
+  </si>
+  <si>
+    <t>required_item_2_name</t>
+  </si>
+  <si>
+    <t>required_item_2_type</t>
+  </si>
+  <si>
+    <t>required_item_2_amount</t>
+  </si>
+  <si>
+    <t>required_item_2_must_be_enchanted</t>
+  </si>
+  <si>
     <t>Welcome to Tlessa</t>
   </si>
   <si>
@@ -1035,6 +1071,129 @@
   </si>
   <si>
     <t>&lt;p&gt;Complete the remaining quests until you reach the end of The Emerald Mirror story line: The beating heart at the center.&lt;/p&gt;&lt;p&gt;Survive a pack size of 10 or greater for 2 or more hours in Delve.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Automating the smithing process</t>
+  </si>
+  <si>
+    <t>You are exhausted, depleted, and emotionally drained from helping the local blacksmith. This is what he does all day, every day. You think to yourself as you sit in the inn: there has to be a better way to do this. You devise a plan to introduce the blacksmith to a form of automation …</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Welcome to Batch Crafting. In this tutorial, we are going to help that blacksmith by batch crafting items for experience. We are going to do this for an hour.&lt;/p&gt;&lt;p&gt;Batch crafting is a system you can learn more about in the help docs. It allows players to automate the levelling experience of crafting, as well as batch craft specific items.&lt;/p&gt;&lt;p&gt;Batch crafted items go to a few different places:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Alchemy items go to your alchemy bag.&lt;/li&gt;&lt;li&gt;Weapons and armour go to a special set called Crafted Items in your inventory. This can hold a maximum of 2,000 items. You may only remove items from here.&lt;/li&gt;&lt;li&gt;Trinkets go in your inventory.&lt;/li&gt;&lt;li&gt;Items you apply holy oils to go into your inventory.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;We will cover this more in the next guide quest. For now, let’s craft and explore.&lt;/p&gt;&lt;p&gt;Crafting and enchanting are such integral aspects of the gear treadmill in Tlessa that you cannot survive on shop gear or found gear for very long. So we are going to speed up our crafting and introduce Batch Crafting.&lt;/p&gt;&lt;p&gt;Keep all the items you craft.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;From the Craft and Enchant drop-down, select Batch Craft. Then leave everything as it is, and select: Keep Highest Level Crafted At The End for disposition.&lt;/p&gt;&lt;p&gt;Click Batch Craft. Might as well also set up some exploration while you’re here, no?&lt;/p&gt;&lt;p&gt;This is going to craft items until one of five things happens:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;You run out of gold.&lt;/li&gt;&lt;li&gt;You run out of crafted inventory space (more on that in the next guide quest).&lt;/li&gt;&lt;li&gt;You die for some reason.&lt;/li&gt;&lt;li&gt;You max out the crafting skill or skills.&lt;/li&gt;&lt;li&gt;You decide to stop it.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;For now, just craft for an hour. You’ll know when to stop it because the guide quest will be ready to hand in.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;From the main option drop-down, select Craft, then Batch Craft. Then leave everything as it is, and select: Keep Highest Level Crafted At The End for disposition.&lt;/p&gt;&lt;p&gt;Click Batch Craft. Might as well also set up some exploration while you’re here, no?&lt;/p&gt;&lt;p&gt;This is going to craft items until one of five things happens:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;You run out of gold.&lt;/li&gt;&lt;li&gt;You run out of crafted inventory space (more on that in the next guide quest).&lt;/li&gt;&lt;li&gt;You die for some reason.&lt;/li&gt;&lt;li&gt;You max out the crafting skill or skills.&lt;/li&gt;&lt;li&gt;You decide to stop it.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;For now, just craft for an hour. You’ll know when to stop it because the guide quest will be ready to hand in.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>craft</t>
+  </si>
+  <si>
+    <t>Effeciency is key</t>
+  </si>
+  <si>
+    <t>The Enchantress and the Blacksmith are quite impressed. As they talk among themselves about the grand plans they have for their individual enterprises, a man appears to move through the shadows. You chase him down to the back alley and see him: young, handsome, and unmistakably the Guide.&lt;br /&gt; &lt;br /&gt; “Why haven’t you been busy?” he scoffs.&lt;br /&gt; &lt;br /&gt; You ask him what he wants, and he states, “I need some weapons and some enchanted armour for a fight I’m going into, a fight to get us some answers. I fear the worst might be true.”&lt;br /&gt; &lt;br /&gt; You have a look of concern on your face but agree anyway, hoping he might tell you something.</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;We have used batch crafting, and we have used batch craft and enchant. Now let’s use the system to create very specific items. First, you will use Craft and batch craft X items. Then you will turn around and do the same thing for Craft and Enchant, but select the item. It does not matter which enchantments you select; the item just has to have two enchants. Once that’s done and the items are in your inventory, the quest will be done.&lt;/p&gt;&lt;p&gt;That’s how we batch craft items, enchant them, and create specific quantities.&lt;/p&gt;&lt;p&gt;I’ll be back again, child, when we do alchemy and dive into holy oils. For now, continue on your journeys.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Just as before, let’s open Batch Craft. This time, select Craft, and then at the bottom, where it says Craft Mode, choose Specific Type and enter the details for the items that do not need enchantments. Let that craft, then do the same thing for Craft and Enchant and fill in the details for the enchanted item.&lt;/p&gt;&lt;p&gt;The enchantments you choose are yours to choose. Just make sure you choose both a prefix and a suffix.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>craft_and_enchant</t>
+  </si>
+  <si>
+    <t>inventory</t>
+  </si>
+  <si>
+    <t>Paladin's Oath Chest</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Diamond Mace</t>
+  </si>
+  <si>
+    <t>Mace</t>
+  </si>
+  <si>
+    <t>A request from The Guide</t>
+  </si>
+  <si>
+    <t>“Mixing potions, are we?” You look up from your studies and see the Guide. What could he want this time? Perhaps answers as to where he went with the weapons and armour you gave him last time?&lt;br /&gt; &lt;br /&gt; You start to ask, but he interrupts you.&lt;br /&gt; &lt;br /&gt; “I need you to figure out how to speed this up. I need items created for this battle.”&lt;br /&gt; &lt;br /&gt; You ask him if he even went to the battle.&lt;br /&gt; &lt;br /&gt; “No, I have been waiting for you to craft something for me. Then I am off!”&lt;br /&gt; &lt;br /&gt; You look confused.</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Remember Batch Crafting? Yeah, we’re going to do that again, but this time for alchemy items. The same principle applies: you can select Keep, Keep the Best, or whatever else. We just need you to do this for an hour.&lt;/p&gt;&lt;p&gt;Batch crafting alchemy items works the same way as crafting or enchanting, but these items go into your Alchemy Bag, which has its own inventory limit of 150 items. You will continue to craft six per minute until you reach the full amount if you choose to keep them. I would sell or keep the highest-level one after that. Up to you.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;By now, we know how to get to Batch Crafting, so let’s select Alchemy from the Crafting Type and choose either Keep Highest Level Crafted At The End or Sell.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>alchemy</t>
+  </si>
+  <si>
+    <t>The alure of The Entranchtress</t>
+  </si>
+  <si>
+    <t>The Enchantress watches you as you manage to craft an item and then manually enchant it. She watches you do this for a while. Maybe you could automate the crafting aspect a bit, like you showed the Blacksmith. It has made his life a lot easier; he can charge top-tier coin for mass-produced, top-tier weapons and armour.&lt;br /&gt; &lt;br /&gt; “Child,” she asks as you stop and look over, “is there not an easier way to do this task?”&lt;br /&gt; &lt;br /&gt; You think for a moment and then smile.</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;So there are two parts to this. First, we have to go to your inventory and see what it created for you. Since you told it to keep only the best, remove those items from your inventory set called Crafted Items. See the instructions for how to do this. These items should end up in your inventory, assuming you have the space, that is.&lt;/p&gt;&lt;p&gt;Next, we’ll combine crafting and enchanting for the next aspect.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Just as before, open Batch Craft. Instead of Craft, in the top select, choose Craft and Enchant and do it for experience. Choose to keep the highest-level crafted item at the end.&lt;/p&gt;&lt;p&gt;Click Batch Craft. Might as well also set up some exploration while you’re here, no?&lt;/p&gt;&lt;p&gt;This is going to craft and then enchant six sets until one of five things happens:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;You run out of gold.&lt;/li&gt;&lt;li&gt;You run out of crafted inventory space (more on that in the next guide quest).&lt;/li&gt;&lt;li&gt;You die for some reason.&lt;/li&gt;&lt;li&gt;You max out the crafting skill or skills.&lt;/li&gt;&lt;li&gt;You decide to stop it.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;For now, just craft and enchant for an hour. You’ll know when to stop it because the guide quest will be ready to hand in.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>More errands for The Guide</t>
+  </si>
+  <si>
+    <t>You whiz through the alchemy items and craft many, basically automating the entire process and making it so much easier. It has been almost two weeks with no sign of the Guide. Just as you’re about to head out for an adventure and wait for him, he appears.&lt;br /&gt; &lt;br /&gt; “Hello, child,” he greets you warmly.&lt;br /&gt; &lt;br /&gt; You step aside and let him in, then ask him what this fight is all about.&lt;br /&gt; &lt;br /&gt; “There is something happening, child. A gate has been found, and until I know more, I have to keep you busy. I need some alchemy items, and I have a list here. Let’s get these created, shall we?”&lt;br /&gt; &lt;br /&gt; You stare at his list and then at him. What are you? His whipping boy?</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Now we know how to craft, craft and enchant, create multiple items, and craft alchemy items. Now we’re going to create very specific alchemy items for the Guide.&lt;/p&gt;&lt;p&gt;Look at what he wants. When you set up alchemy, choose Keep and Craft Amount to craft a specific amount.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;When setting up alchemy for batch crafting, select Keep, select Specific Amount, and create what the Guide wants.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>alchemy_bag</t>
+  </si>
+  <si>
+    <t>Mixtures and Concoctions</t>
+  </si>
+  <si>
+    <t>Increases Alchemy Skill</t>
+  </si>
+  <si>
+    <t>The Gates Are Opening</t>
+  </si>
+  <si>
+    <t>You’re sitting alone in a room in an abandoned house, trying to recover from the last adventure you were on and mending your wounds, when an older man’s voice appears out of nowhere and a man walks from the shadows.&lt;br /&gt; &lt;br /&gt; “Have you seen where I put my oils? My gear isn’t holding up in this fight.”&lt;br /&gt; &lt;br /&gt; You look more closely and realize it is the Guide, but older and more frail-looking. You ask him what happened.&lt;br /&gt; &lt;br /&gt; “The gates, child. They are opening. He will walk again, and chaos will come.”&lt;br /&gt; &lt;br /&gt; You look at him with shock on your face.&lt;br /&gt; &lt;br /&gt; “Alas, you are not prepared yet to handle what comes once those gates are opened. However, you can be. You’ll need some oil and some gear.”</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;By now, you have applied some holy oils to your equipment, but did you know you can do this in batch? Yes, you can use Batch Craft to do this by selecting Holy Oils.&lt;/p&gt;&lt;p&gt;This will take the oils and apply them to selected gear until all the holy stacks on the items are filled, or until you run out of currencies or oils.&lt;/p&gt;&lt;p&gt;So you’ll need to craft some oils. Might as well batch craft that, and then use the Holy Oils section to apply the oils to your selected items. As long as you have the required holy stacks, you are good no matter how you do this.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Use batch crafting if needed to craft some items.&lt;/li&gt;&lt;li&gt;Use Craft Amount on alchemy items to craft some oils.&lt;/li&gt;&lt;li&gt;Use Holy Oils from Batch Crafting to select the items and the oils, then start the process.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>Where do we go from here?</t>
+  </si>
+  <si>
+    <t>You stand before an old altar in ruins in the middle of nowhere. The shadows of your mind dance around, and you see it clearly before you: a vision.&lt;br /&gt; &lt;br /&gt; Before you stands the Guide, bloodied and broken. His voice reaches out across time and space, echoing in your ear: “Child, the gates are opening. The prince will walk. I need you to hurry up with those damn trinkets …”</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;The last aspect of Batch Crafting is Trinketry. These will appear in your Crafted Items set, and we will craft six at a time for experience. You can’t craft multiples of these because it doesn’t make sense, so you might as well keep the best one.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Use batch crafting to craft trinkets for experience. Keep the best one, and do this for an hour.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>trinketry</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1533,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BH51"/>
+  <dimension ref="A1:BT58"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="3.428" bestFit="true" customWidth="true" style="0"/>
@@ -1437,9 +1596,21 @@
     <col min="58" max="58" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="59" max="59" width="34.135" bestFit="true" customWidth="true" style="0"/>
     <col min="60" max="60" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="61" max="61" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="62" max="62" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="63" max="63" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="64" max="64" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="65" max="65" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="66" max="66" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="67" max="67" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="68" max="68" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="69" max="69" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="70" max="70" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="71" max="71" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="72" max="72" width="39.99" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:72">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1611,25 +1782,61 @@
       <c r="BH1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:72">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1641,30 +1848,30 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:60">
+    <row r="3" spans="1:72">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="Q3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1676,36 +1883,36 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:60">
+    <row r="4" spans="1:72">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G4">
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -1720,45 +1927,45 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:60">
+    <row r="5" spans="1:72">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="U5" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="V5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AS5">
         <v>1000</v>
@@ -1767,42 +1974,42 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:72">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G6">
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="U6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AM6">
         <v>125</v>
@@ -1814,36 +2021,36 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:60">
+    <row r="7" spans="1:72">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="G7">
         <v>120</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J7">
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1855,7 +2062,7 @@
         <v>10</v>
       </c>
       <c r="U7" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="X7">
         <v>500</v>
@@ -1876,33 +2083,33 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:60">
+    <row r="8" spans="1:72">
       <c r="A8">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="Q8" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="T8" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="AQ8">
         <v>1000</v>
@@ -1917,33 +2124,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:60">
+    <row r="9" spans="1:72">
       <c r="A9">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>50</v>
       </c>
       <c r="T9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AQ9">
         <v>2500</v>
@@ -1958,39 +2165,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:60">
+    <row r="10" spans="1:72">
       <c r="A10">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G10">
         <v>300</v>
       </c>
       <c r="Q10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="R10">
         <v>2</v>
       </c>
       <c r="S10" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="U10" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="AQ10">
         <v>1000</v>
@@ -2002,24 +2209,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:60">
+    <row r="11" spans="1:72">
       <c r="A11">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -2034,24 +2241,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:60">
+    <row r="12" spans="1:72">
       <c r="A12">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="AB12">
         <v>1</v>
@@ -2069,33 +2276,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:60">
+    <row r="13" spans="1:72">
       <c r="A13">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F13" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J13">
         <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -2107,7 +2314,7 @@
         <v>500</v>
       </c>
       <c r="AG13" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="AH13">
         <v>1</v>
@@ -2119,24 +2326,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:60">
+    <row r="14" spans="1:72">
       <c r="A14">
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AC14">
         <v>75</v>
@@ -2145,7 +2352,7 @@
         <v>2000</v>
       </c>
       <c r="AG14" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AH14">
         <v>2</v>
@@ -2157,33 +2364,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:60">
+    <row r="15" spans="1:72">
       <c r="A15">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I15" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J15">
         <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L15">
         <v>50</v>
@@ -2195,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="T15" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="AC15">
         <v>100</v>
@@ -2204,7 +2411,7 @@
         <v>3000</v>
       </c>
       <c r="AG15" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AH15">
         <v>1</v>
@@ -2216,36 +2423,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:60">
+    <row r="16" spans="1:72">
       <c r="A16">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G16">
         <v>500</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L16">
         <v>50</v>
@@ -2257,22 +2464,22 @@
         <v>100</v>
       </c>
       <c r="Q16" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="R16">
         <v>3</v>
       </c>
       <c r="S16" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="T16" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="U16" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="V16" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="X16">
         <v>25000</v>
@@ -2287,30 +2494,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:60">
+    <row r="17" spans="1:72">
       <c r="A17">
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G17">
         <v>600</v>
       </c>
       <c r="I17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -2334,30 +2541,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:60">
+    <row r="18" spans="1:72">
       <c r="A18">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G18">
         <v>1000</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L18">
         <v>400</v>
@@ -2375,7 +2582,7 @@
         <v>30</v>
       </c>
       <c r="T18" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AI18">
         <v>6000</v>
@@ -2393,39 +2600,39 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:60">
+    <row r="19" spans="1:72">
       <c r="A19">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F19" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G19">
         <v>1500</v>
       </c>
       <c r="Q19" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="U19" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AI19">
         <v>7000</v>
@@ -2437,30 +2644,30 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:60">
+    <row r="20" spans="1:72">
       <c r="A20">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G20">
         <v>2000</v>
       </c>
       <c r="T20" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="AS20">
         <v>2000000000</v>
@@ -2469,30 +2676,30 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:60">
+    <row r="21" spans="1:72">
       <c r="A21">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G21">
         <v>2500</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J21">
         <v>50</v>
@@ -2504,7 +2711,7 @@
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2519,7 +2726,7 @@
         <v>20000</v>
       </c>
       <c r="AE21" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AF21">
         <v>5</v>
@@ -2537,24 +2744,24 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:60">
+    <row r="22" spans="1:72">
       <c r="A22">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F22" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AS22">
         <v>100000</v>
@@ -2569,27 +2776,27 @@
         <v>3</v>
       </c>
       <c r="BA22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:60">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:72">
       <c r="A23">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F23" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AS23">
         <v>100000</v>
@@ -2598,7 +2805,7 @@
         <v>75</v>
       </c>
       <c r="AU23" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AW23">
         <v>25</v>
@@ -2610,27 +2817,27 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:60">
+    <row r="24" spans="1:72">
       <c r="A24">
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F24" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="T24" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AQ24">
         <v>5000</v>
@@ -2645,7 +2852,7 @@
         <v>100</v>
       </c>
       <c r="AU24" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AW24">
         <v>25</v>
@@ -2654,27 +2861,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:60">
+    <row r="25" spans="1:72">
       <c r="A25">
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D25" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E25" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="T25" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AQ25">
         <v>1000</v>
@@ -2689,7 +2896,7 @@
         <v>100</v>
       </c>
       <c r="AU25" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="AW25">
         <v>25</v>
@@ -2698,27 +2905,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:60">
+    <row r="26" spans="1:72">
       <c r="A26">
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C26" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F26" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="T26" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AQ26">
         <v>2000</v>
@@ -2733,7 +2940,7 @@
         <v>100</v>
       </c>
       <c r="AU26" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AW26">
         <v>25</v>
@@ -2742,27 +2949,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:60">
+    <row r="27" spans="1:72">
       <c r="A27">
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D27" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E27" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F27" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="T27" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AB27">
         <v>1</v>
@@ -2774,7 +2981,7 @@
         <v>500</v>
       </c>
       <c r="AG27" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="AH27">
         <v>1</v>
@@ -2792,7 +2999,7 @@
         <v>100</v>
       </c>
       <c r="AU27" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AW27">
         <v>25</v>
@@ -2801,33 +3008,33 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:60">
+    <row r="28" spans="1:72">
       <c r="A28">
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E28" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F28" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="S28" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="T28" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="U28" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AQ28">
         <v>25000</v>
@@ -2842,30 +3049,30 @@
         <v>2000</v>
       </c>
       <c r="BA28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:60">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:72">
       <c r="A29">
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E29" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F29" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="Q29" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -2883,30 +3090,30 @@
         <v>2000</v>
       </c>
       <c r="BE29" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:60">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:72">
       <c r="A30">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E30" t="s">
+        <v>239</v>
+      </c>
+      <c r="F30" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q30" t="s">
         <v>227</v>
-      </c>
-      <c r="F30" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>215</v>
       </c>
       <c r="R30">
         <v>5</v>
@@ -2924,30 +3131,30 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="1:60">
+    <row r="31" spans="1:72">
       <c r="A31">
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F31" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="S31" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="T31" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AQ31">
         <v>25000</v>
@@ -2962,30 +3169,30 @@
         <v>2000</v>
       </c>
       <c r="BA31" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="1:60">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="32" spans="1:72">
       <c r="A32">
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C32" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E32" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="J32">
         <v>200</v>
@@ -3003,27 +3210,27 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="1:60">
+    <row r="33" spans="1:72">
       <c r="A33">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E33" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="T33" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Z33">
         <v>5000</v>
@@ -3044,24 +3251,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:60">
+    <row r="34" spans="1:72">
       <c r="A34">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D34" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E34" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F34" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AQ34">
         <v>50000</v>
@@ -3076,30 +3283,30 @@
         <v>5000</v>
       </c>
       <c r="BE34" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="35" spans="1:60">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:72">
       <c r="A35">
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C35" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D35" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E35" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F35" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="I35" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J35">
         <v>25</v>
@@ -3117,27 +3324,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="36" spans="1:60">
+    <row r="36" spans="1:72">
       <c r="A36">
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D36" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E36" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F36" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="Q36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="R36">
         <v>5</v>
@@ -3161,33 +3368,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:60">
+    <row r="37" spans="1:72">
       <c r="A37">
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="D37" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="E37" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F37" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="I37" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J37">
         <v>75</v>
       </c>
       <c r="T37" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AQ37">
         <v>150000</v>
@@ -3202,27 +3409,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="38" spans="1:60">
+    <row r="38" spans="1:72">
       <c r="A38">
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C38" t="s">
+        <v>279</v>
+      </c>
+      <c r="D38" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" t="s">
+        <v>281</v>
+      </c>
+      <c r="F38" t="s">
+        <v>282</v>
+      </c>
+      <c r="I38" t="s">
         <v>267</v>
-      </c>
-      <c r="D38" t="s">
-        <v>268</v>
-      </c>
-      <c r="E38" t="s">
-        <v>269</v>
-      </c>
-      <c r="F38" t="s">
-        <v>270</v>
-      </c>
-      <c r="I38" t="s">
-        <v>255</v>
       </c>
       <c r="J38">
         <v>150</v>
@@ -3243,13 +3450,13 @@
         <v>50000</v>
       </c>
       <c r="AE38" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AF38">
         <v>30</v>
       </c>
       <c r="AG38" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AH38">
         <v>4</v>
@@ -3267,27 +3474,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="39" spans="1:60">
+    <row r="39" spans="1:72">
       <c r="A39">
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D39" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="E39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="F39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I39" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J39">
         <v>300</v>
@@ -3308,36 +3515,36 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="40" spans="1:60">
+    <row r="40" spans="1:72">
       <c r="A40">
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E40" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F40" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="I40" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J40">
         <v>400</v>
       </c>
       <c r="T40" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="U40" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="AI40">
         <v>2000000</v>
@@ -3355,24 +3562,24 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="41" spans="1:60">
+    <row r="41" spans="1:72">
       <c r="A41">
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D41" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E41" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="F41" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AI41">
         <v>2500000</v>
@@ -3390,27 +3597,27 @@
         <v>8000</v>
       </c>
       <c r="BA41" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:60">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="42" spans="1:72">
       <c r="A42">
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C42" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D42" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="E42" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F42" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AQ42">
         <v>100</v>
@@ -3431,27 +3638,27 @@
         <v>7</v>
       </c>
       <c r="BA42" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="43" spans="1:60">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:72">
       <c r="A43">
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C43" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="E43" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="F43" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AQ43">
         <v>100</v>
@@ -3466,39 +3673,39 @@
         <v>100</v>
       </c>
       <c r="AU43" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="AY43">
         <v>7</v>
       </c>
       <c r="BA43" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="BB43">
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:60">
+    <row r="44" spans="1:72">
       <c r="A44">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E44" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F44" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="T44" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="AQ44">
         <v>100</v>
@@ -3513,36 +3720,36 @@
         <v>100</v>
       </c>
       <c r="AU44" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AY44">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:60">
+    <row r="45" spans="1:72">
       <c r="A45">
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C45" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="F45" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="T45" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="U45" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="AQ45">
         <v>100</v>
@@ -3557,33 +3764,33 @@
         <v>100</v>
       </c>
       <c r="AU45" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="AY45">
         <v>7</v>
       </c>
       <c r="BA45" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:60">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:72">
       <c r="A46">
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C46" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D46" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F46" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="H46">
         <v>10</v>
@@ -3601,33 +3808,33 @@
         <v>2500</v>
       </c>
       <c r="AU46" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="47" spans="1:60">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="47" spans="1:72">
       <c r="A47">
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D47" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E47" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="S47" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="T47" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AQ47">
         <v>100000</v>
@@ -3642,33 +3849,33 @@
         <v>10000</v>
       </c>
       <c r="AU47" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="48" spans="1:60">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="48" spans="1:72">
       <c r="A48">
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C48" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="D48" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E48" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F48" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="T48" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="U48" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="AQ48">
         <v>10000</v>
@@ -3683,27 +3890,27 @@
         <v>10000</v>
       </c>
       <c r="AU48" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="49" spans="1:60">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="49" spans="1:72">
       <c r="A49">
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C49" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D49" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E49" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F49" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AQ49">
         <v>100000</v>
@@ -3718,33 +3925,33 @@
         <v>25000</v>
       </c>
       <c r="AU49" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="BG49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:60">
+    <row r="50" spans="1:72">
       <c r="A50">
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C50" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D50" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E50" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F50" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="U50" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="AQ50">
         <v>200000</v>
@@ -3759,7 +3966,7 @@
         <v>30000</v>
       </c>
       <c r="AU50" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="BG50">
         <v>1</v>
@@ -3768,24 +3975,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:60">
+    <row r="51" spans="1:72">
       <c r="A51">
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C51" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D51" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E51" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F51" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="AQ51">
         <v>500000</v>
@@ -3800,13 +4007,336 @@
         <v>125000</v>
       </c>
       <c r="AU51" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="BG51">
         <v>2</v>
       </c>
       <c r="BH51">
         <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:72">
+      <c r="A52">
+        <v>57</v>
+      </c>
+      <c r="B52" t="s">
+        <v>352</v>
+      </c>
+      <c r="C52" t="s">
+        <v>353</v>
+      </c>
+      <c r="D52" t="s">
+        <v>354</v>
+      </c>
+      <c r="E52" t="s">
+        <v>355</v>
+      </c>
+      <c r="F52" t="s">
+        <v>356</v>
+      </c>
+      <c r="AQ52">
+        <v>2500</v>
+      </c>
+      <c r="AR52">
+        <v>1000</v>
+      </c>
+      <c r="AS52">
+        <v>2500</v>
+      </c>
+      <c r="AT52">
+        <v>150</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI52" t="s">
+        <v>357</v>
+      </c>
+      <c r="BJ52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:72">
+      <c r="A53">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>358</v>
+      </c>
+      <c r="C53" t="s">
+        <v>359</v>
+      </c>
+      <c r="D53" t="s">
+        <v>360</v>
+      </c>
+      <c r="E53" t="s">
+        <v>361</v>
+      </c>
+      <c r="F53" t="s">
+        <v>361</v>
+      </c>
+      <c r="AQ53">
+        <v>5000</v>
+      </c>
+      <c r="AR53">
+        <v>5000</v>
+      </c>
+      <c r="AS53">
+        <v>25000</v>
+      </c>
+      <c r="AT53">
+        <v>200</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>96</v>
+      </c>
+      <c r="BI53" t="s">
+        <v>362</v>
+      </c>
+      <c r="BJ53">
+        <v>1</v>
+      </c>
+      <c r="BK53" t="s">
+        <v>363</v>
+      </c>
+      <c r="BL53" t="s">
+        <v>364</v>
+      </c>
+      <c r="BM53" t="s">
+        <v>365</v>
+      </c>
+      <c r="BN53">
+        <v>15</v>
+      </c>
+      <c r="BO53">
+        <v>1</v>
+      </c>
+      <c r="BP53" t="s">
+        <v>363</v>
+      </c>
+      <c r="BQ53" t="s">
+        <v>366</v>
+      </c>
+      <c r="BR53" t="s">
+        <v>367</v>
+      </c>
+      <c r="BS53">
+        <v>20</v>
+      </c>
+      <c r="BT53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:72">
+      <c r="A54">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>368</v>
+      </c>
+      <c r="C54" t="s">
+        <v>369</v>
+      </c>
+      <c r="D54" t="s">
+        <v>370</v>
+      </c>
+      <c r="E54" t="s">
+        <v>371</v>
+      </c>
+      <c r="F54" t="s">
+        <v>371</v>
+      </c>
+      <c r="AQ54">
+        <v>5000</v>
+      </c>
+      <c r="AR54">
+        <v>5000</v>
+      </c>
+      <c r="AS54">
+        <v>20000</v>
+      </c>
+      <c r="AT54">
+        <v>500</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>187</v>
+      </c>
+      <c r="BI54" t="s">
+        <v>372</v>
+      </c>
+      <c r="BJ54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:72">
+      <c r="A55">
+        <v>60</v>
+      </c>
+      <c r="B55" t="s">
+        <v>373</v>
+      </c>
+      <c r="C55" t="s">
+        <v>374</v>
+      </c>
+      <c r="D55" t="s">
+        <v>375</v>
+      </c>
+      <c r="E55" t="s">
+        <v>376</v>
+      </c>
+      <c r="F55" t="s">
+        <v>376</v>
+      </c>
+      <c r="AQ55">
+        <v>2000</v>
+      </c>
+      <c r="AR55">
+        <v>1000</v>
+      </c>
+      <c r="AS55">
+        <v>175</v>
+      </c>
+      <c r="AT55">
+        <v>175</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI55" t="s">
+        <v>362</v>
+      </c>
+      <c r="BJ55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:72">
+      <c r="A56">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>377</v>
+      </c>
+      <c r="C56" t="s">
+        <v>378</v>
+      </c>
+      <c r="D56" t="s">
+        <v>379</v>
+      </c>
+      <c r="E56" t="s">
+        <v>380</v>
+      </c>
+      <c r="F56" t="s">
+        <v>380</v>
+      </c>
+      <c r="AQ56">
+        <v>5000</v>
+      </c>
+      <c r="AR56">
+        <v>5000</v>
+      </c>
+      <c r="AS56">
+        <v>10000</v>
+      </c>
+      <c r="AT56">
+        <v>1000</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>368</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>381</v>
+      </c>
+      <c r="BL56" t="s">
+        <v>382</v>
+      </c>
+      <c r="BM56" t="s">
+        <v>383</v>
+      </c>
+      <c r="BN56">
+        <v>25</v>
+      </c>
+      <c r="BO56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:72">
+      <c r="A57">
+        <v>62</v>
+      </c>
+      <c r="B57" t="s">
+        <v>384</v>
+      </c>
+      <c r="C57" t="s">
+        <v>385</v>
+      </c>
+      <c r="D57" t="s">
+        <v>386</v>
+      </c>
+      <c r="E57" t="s">
+        <v>387</v>
+      </c>
+      <c r="F57" t="s">
+        <v>387</v>
+      </c>
+      <c r="AQ57">
+        <v>5000</v>
+      </c>
+      <c r="AR57">
+        <v>5000</v>
+      </c>
+      <c r="AS57">
+        <v>2000</v>
+      </c>
+      <c r="AT57">
+        <v>350</v>
+      </c>
+      <c r="AU57" t="s">
+        <v>251</v>
+      </c>
+      <c r="BC57">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:72">
+      <c r="A58">
+        <v>63</v>
+      </c>
+      <c r="B58" t="s">
+        <v>388</v>
+      </c>
+      <c r="C58" t="s">
+        <v>389</v>
+      </c>
+      <c r="D58" t="s">
+        <v>390</v>
+      </c>
+      <c r="E58" t="s">
+        <v>391</v>
+      </c>
+      <c r="F58" t="s">
+        <v>391</v>
+      </c>
+      <c r="AQ58">
+        <v>10000</v>
+      </c>
+      <c r="AR58">
+        <v>10000</v>
+      </c>
+      <c r="AS58">
+        <v>80000</v>
+      </c>
+      <c r="AT58">
+        <v>1000</v>
+      </c>
+      <c r="AU58" t="s">
+        <v>176</v>
+      </c>
+      <c r="BI58" t="s">
+        <v>392</v>
+      </c>
+      <c r="BJ58">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resources/data-imports/Quests/guide-quests.xlsx
+++ b/resources/data-imports/Quests/guide-quests.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="395">
   <si>
     <t>id</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>required_event_goal_participation</t>
+  </si>
+  <si>
+    <t>required_event_goal_crafting_participation</t>
+  </si>
+  <si>
+    <t>required_event_goal_enchanting_participation</t>
   </si>
   <si>
     <t>required_holy_stacks</t>
@@ -1533,7 +1539,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:BT58"/>
+  <dimension ref="A1:BS58"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="3.428" bestFit="true" customWidth="true" style="0"/>
@@ -1583,34 +1589,33 @@
     <col min="45" max="45" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="46" max="46" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="47" max="47" width="43.561" bestFit="true" customWidth="true" style="0"/>
-    <col min="48" max="48" width="9.10" bestFit="true" style="0"/>
-    <col min="49" max="49" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="50" max="50" width="9.10" bestFit="true" style="0"/>
-    <col min="51" max="51" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="52" max="52" width="9.10" bestFit="true" style="0"/>
-    <col min="53" max="53" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="54" max="54" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="55" max="55" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="56" max="56" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="57" max="57" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="58" max="58" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="59" max="59" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="60" max="60" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="61" max="61" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="62" max="62" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="63" max="63" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="64" max="64" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="65" max="65" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="66" max="66" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="67" max="67" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="68" max="68" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="48" max="48" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="49" max="49" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="50" max="50" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="51" max="51" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="52" max="52" width="50.559" bestFit="true" customWidth="true" style="0"/>
+    <col min="53" max="53" width="52.987" bestFit="true" customWidth="true" style="0"/>
+    <col min="54" max="54" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="55" max="55" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="56" max="56" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="57" max="57" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="58" max="58" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="59" max="59" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="60" max="60" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="61" max="61" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="62" max="62" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="63" max="63" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="64" max="64" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="65" max="65" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="66" max="66" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="67" max="67" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="68" max="68" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="69" max="69" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="70" max="70" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="71" max="71" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="72" max="72" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="70" max="70" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="71" max="71" width="39.99" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72">
+    <row r="1" spans="1:71">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1752,91 +1757,97 @@
       <c r="AU1" t="s">
         <v>46</v>
       </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
       <c r="AW1" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
       </c>
       <c r="AY1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
       </c>
       <c r="BA1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="BB1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BJ1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BK1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="BL1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="BM1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="BN1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="BO1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="BP1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="BQ1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="BR1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BS1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:71">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1848,30 +1859,30 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:72">
+    <row r="3" spans="1:71">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1883,36 +1894,36 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:72">
+    <row r="4" spans="1:71">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J4">
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -1927,45 +1938,45 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:72">
+    <row r="5" spans="1:71">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="U5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AS5">
         <v>1000</v>
@@ -1974,42 +1985,42 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:72">
+    <row r="6" spans="1:71">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G6">
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6">
         <v>15</v>
       </c>
       <c r="U6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AM6">
         <v>125</v>
@@ -2021,36 +2032,36 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:72">
+    <row r="7" spans="1:71">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G7">
         <v>120</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J7">
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -2062,7 +2073,7 @@
         <v>10</v>
       </c>
       <c r="U7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X7">
         <v>500</v>
@@ -2083,33 +2094,33 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:72">
+    <row r="8" spans="1:71">
       <c r="A8">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="T8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AQ8">
         <v>1000</v>
@@ -2124,33 +2135,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:72">
+    <row r="9" spans="1:71">
       <c r="A9">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J9">
         <v>50</v>
       </c>
       <c r="T9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AQ9">
         <v>2500</v>
@@ -2165,39 +2176,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:72">
+    <row r="10" spans="1:71">
       <c r="A10">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G10">
         <v>300</v>
       </c>
       <c r="Q10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R10">
         <v>2</v>
       </c>
       <c r="S10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="U10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AQ10">
         <v>1000</v>
@@ -2209,24 +2220,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:72">
+    <row r="11" spans="1:71">
       <c r="A11">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -2241,24 +2252,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:72">
+    <row r="12" spans="1:71">
       <c r="A12">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AB12">
         <v>1</v>
@@ -2276,33 +2287,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:72">
+    <row r="13" spans="1:71">
       <c r="A13">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13">
         <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -2314,7 +2325,7 @@
         <v>500</v>
       </c>
       <c r="AG13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH13">
         <v>1</v>
@@ -2326,24 +2337,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:72">
+    <row r="14" spans="1:71">
       <c r="A14">
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AC14">
         <v>75</v>
@@ -2352,7 +2363,7 @@
         <v>2000</v>
       </c>
       <c r="AG14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AH14">
         <v>2</v>
@@ -2364,33 +2375,33 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:72">
+    <row r="15" spans="1:71">
       <c r="A15">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J15">
         <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L15">
         <v>50</v>
@@ -2402,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="T15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AC15">
         <v>100</v>
@@ -2411,7 +2422,7 @@
         <v>3000</v>
       </c>
       <c r="AG15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AH15">
         <v>1</v>
@@ -2423,36 +2434,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:72">
+    <row r="16" spans="1:71">
       <c r="A16">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G16">
         <v>500</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L16">
         <v>50</v>
@@ -2464,22 +2475,22 @@
         <v>100</v>
       </c>
       <c r="Q16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R16">
         <v>3</v>
       </c>
       <c r="S16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="X16">
         <v>25000</v>
@@ -2494,30 +2505,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:72">
+    <row r="17" spans="1:71">
       <c r="A17">
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G17">
         <v>600</v>
       </c>
       <c r="I17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -2541,30 +2552,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:72">
+    <row r="18" spans="1:71">
       <c r="A18">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G18">
         <v>1000</v>
       </c>
       <c r="K18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L18">
         <v>400</v>
@@ -2582,7 +2593,7 @@
         <v>30</v>
       </c>
       <c r="T18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AI18">
         <v>6000</v>
@@ -2600,39 +2611,39 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:72">
+    <row r="19" spans="1:71">
       <c r="A19">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G19">
         <v>1500</v>
       </c>
       <c r="Q19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="U19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AI19">
         <v>7000</v>
@@ -2644,30 +2655,30 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:72">
+    <row r="20" spans="1:71">
       <c r="A20">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G20">
         <v>2000</v>
       </c>
       <c r="T20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AS20">
         <v>2000000000</v>
@@ -2676,30 +2687,30 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="1:72">
+    <row r="21" spans="1:71">
       <c r="A21">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G21">
         <v>2500</v>
       </c>
       <c r="I21" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J21">
         <v>50</v>
@@ -2711,7 +2722,7 @@
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2726,7 +2737,7 @@
         <v>20000</v>
       </c>
       <c r="AE21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AF21">
         <v>5</v>
@@ -2744,24 +2755,24 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:72">
+    <row r="22" spans="1:71">
       <c r="A22">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AS22">
         <v>100000</v>
@@ -2769,34 +2780,34 @@
       <c r="AT22">
         <v>50</v>
       </c>
+      <c r="AV22">
+        <v>25</v>
+      </c>
       <c r="AW22">
-        <v>25</v>
-      </c>
-      <c r="AY22">
         <v>3</v>
       </c>
-      <c r="BA22" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" spans="1:72">
+      <c r="AX22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:71">
       <c r="A23">
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AS23">
         <v>100000</v>
@@ -2805,39 +2816,39 @@
         <v>75</v>
       </c>
       <c r="AU23" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="AV23">
+        <v>25</v>
       </c>
       <c r="AW23">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AY23">
-        <v>3</v>
-      </c>
-      <c r="BB23">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" spans="1:72">
+    <row r="24" spans="1:71">
       <c r="A24">
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C24" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F24" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T24" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AQ24">
         <v>5000</v>
@@ -2852,36 +2863,36 @@
         <v>100</v>
       </c>
       <c r="AU24" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="AV24">
+        <v>25</v>
       </c>
       <c r="AW24">
-        <v>25</v>
-      </c>
-      <c r="AY24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:72">
+    <row r="25" spans="1:71">
       <c r="A25">
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="T25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AQ25">
         <v>1000</v>
@@ -2896,36 +2907,36 @@
         <v>100</v>
       </c>
       <c r="AU25" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="AV25">
+        <v>25</v>
       </c>
       <c r="AW25">
-        <v>25</v>
-      </c>
-      <c r="AY25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:72">
+    <row r="26" spans="1:71">
       <c r="A26">
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D26" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E26" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="T26" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AQ26">
         <v>2000</v>
@@ -2940,36 +2951,36 @@
         <v>100</v>
       </c>
       <c r="AU26" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="AV26">
+        <v>25</v>
       </c>
       <c r="AW26">
-        <v>25</v>
-      </c>
-      <c r="AY26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:72">
+    <row r="27" spans="1:71">
       <c r="A27">
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E27" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AB27">
         <v>1</v>
@@ -2981,7 +2992,7 @@
         <v>500</v>
       </c>
       <c r="AG27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AH27">
         <v>1</v>
@@ -2999,42 +3010,42 @@
         <v>100</v>
       </c>
       <c r="AU27" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="AV27">
+        <v>25</v>
       </c>
       <c r="AW27">
-        <v>25</v>
-      </c>
-      <c r="AY27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:72">
+    <row r="28" spans="1:71">
       <c r="A28">
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="T28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="U28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AQ28">
         <v>25000</v>
@@ -3048,31 +3059,31 @@
       <c r="AT28">
         <v>2000</v>
       </c>
-      <c r="BA28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:72">
+      <c r="AX28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:71">
       <c r="A29">
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q29" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -3089,31 +3100,31 @@
       <c r="AT29">
         <v>2000</v>
       </c>
-      <c r="BE29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:72">
+      <c r="BD29" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:71">
       <c r="A30">
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F30" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R30">
         <v>5</v>
@@ -3131,30 +3142,30 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="1:72">
+    <row r="31" spans="1:71">
       <c r="A31">
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D31" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F31" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="S31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="T31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AQ31">
         <v>25000</v>
@@ -3168,31 +3179,31 @@
       <c r="AT31">
         <v>2000</v>
       </c>
-      <c r="BA31" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="32" spans="1:72">
+      <c r="AX31" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" spans="1:71">
       <c r="A32">
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D32" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F32" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J32">
         <v>200</v>
@@ -3210,27 +3221,27 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="1:72">
+    <row r="33" spans="1:71">
       <c r="A33">
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D33" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F33" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="T33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Z33">
         <v>5000</v>
@@ -3247,28 +3258,28 @@
       <c r="AT33">
         <v>5000</v>
       </c>
-      <c r="BC33">
+      <c r="BB33">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:72">
+    <row r="34" spans="1:71">
       <c r="A34">
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E34" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F34" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AQ34">
         <v>50000</v>
@@ -3282,31 +3293,31 @@
       <c r="AT34">
         <v>5000</v>
       </c>
-      <c r="BE34" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:72">
+      <c r="BD34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:71">
       <c r="A35">
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C35" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D35" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E35" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F35" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I35" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J35">
         <v>25</v>
@@ -3324,27 +3335,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="36" spans="1:72">
+    <row r="36" spans="1:71">
       <c r="A36">
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C36" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D36" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F36" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R36">
         <v>5</v>
@@ -3361,40 +3372,40 @@
       <c r="AT36">
         <v>100</v>
       </c>
-      <c r="AW36">
+      <c r="AV36">
         <v>1500</v>
       </c>
-      <c r="BF36">
+      <c r="BE36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:72">
+    <row r="37" spans="1:71">
       <c r="A37">
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D37" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J37">
         <v>75</v>
       </c>
       <c r="T37" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AQ37">
         <v>150000</v>
@@ -3409,27 +3420,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="38" spans="1:72">
+    <row r="38" spans="1:71">
       <c r="A38">
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C38" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D38" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F38" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J38">
         <v>150</v>
@@ -3450,13 +3461,13 @@
         <v>50000</v>
       </c>
       <c r="AE38" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AF38">
         <v>30</v>
       </c>
       <c r="AG38" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AH38">
         <v>4</v>
@@ -3474,27 +3485,27 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="39" spans="1:72">
+    <row r="39" spans="1:71">
       <c r="A39">
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C39" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D39" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F39" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J39">
         <v>300</v>
@@ -3515,36 +3526,36 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="40" spans="1:72">
+    <row r="40" spans="1:71">
       <c r="A40">
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E40" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F40" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I40" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J40">
         <v>400</v>
       </c>
       <c r="T40" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="U40" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AI40">
         <v>2000000</v>
@@ -3562,24 +3573,24 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="41" spans="1:72">
+    <row r="41" spans="1:71">
       <c r="A41">
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C41" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E41" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AI41">
         <v>2500000</v>
@@ -3596,28 +3607,28 @@
       <c r="AT41">
         <v>8000</v>
       </c>
-      <c r="BA41" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="42" spans="1:72">
+      <c r="AX41" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:71">
       <c r="A42">
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ42">
         <v>100</v>
@@ -3631,34 +3642,34 @@
       <c r="AT42">
         <v>100</v>
       </c>
+      <c r="AV42">
+        <v>10</v>
+      </c>
       <c r="AW42">
-        <v>10</v>
-      </c>
-      <c r="AY42">
         <v>7</v>
       </c>
-      <c r="BA42" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="43" spans="1:72">
+      <c r="AX42" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="43" spans="1:71">
       <c r="A43">
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D43" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E43" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ43">
         <v>100</v>
@@ -3673,39 +3684,39 @@
         <v>100</v>
       </c>
       <c r="AU43" t="s">
-        <v>300</v>
+        <v>302</v>
+      </c>
+      <c r="AW43">
+        <v>7</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>307</v>
       </c>
       <c r="AY43">
-        <v>7</v>
-      </c>
-      <c r="BA43" t="s">
-        <v>305</v>
-      </c>
-      <c r="BB43">
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:72">
+    <row r="44" spans="1:71">
       <c r="A44">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D44" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E44" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F44" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="T44" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AQ44">
         <v>100</v>
@@ -3720,36 +3731,36 @@
         <v>100</v>
       </c>
       <c r="AU44" t="s">
-        <v>306</v>
-      </c>
-      <c r="AY44">
+        <v>308</v>
+      </c>
+      <c r="AW44">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:72">
+    <row r="45" spans="1:71">
       <c r="A45">
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C45" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D45" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="T45" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U45" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AQ45">
         <v>100</v>
@@ -3764,33 +3775,33 @@
         <v>100</v>
       </c>
       <c r="AU45" t="s">
-        <v>311</v>
-      </c>
-      <c r="AY45">
+        <v>313</v>
+      </c>
+      <c r="AW45">
         <v>7</v>
       </c>
-      <c r="BA45" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:72">
+      <c r="AX45" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:71">
       <c r="A46">
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C46" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D46" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E46" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F46" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H46">
         <v>10</v>
@@ -3808,33 +3819,33 @@
         <v>2500</v>
       </c>
       <c r="AU46" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="47" spans="1:72">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:71">
       <c r="A47">
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D47" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S47" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="T47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AQ47">
         <v>100000</v>
@@ -3849,33 +3860,33 @@
         <v>10000</v>
       </c>
       <c r="AU47" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="48" spans="1:72">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="48" spans="1:71">
       <c r="A48">
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C48" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D48" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F48" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T48" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="U48" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ48">
         <v>10000</v>
@@ -3890,27 +3901,27 @@
         <v>10000</v>
       </c>
       <c r="AU48" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="49" spans="1:72">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:71">
       <c r="A49">
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C49" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E49" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F49" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AQ49">
         <v>100000</v>
@@ -3925,33 +3936,33 @@
         <v>25000</v>
       </c>
       <c r="AU49" t="s">
-        <v>332</v>
-      </c>
-      <c r="BG49">
+        <v>334</v>
+      </c>
+      <c r="BF49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:72">
+    <row r="50" spans="1:71">
       <c r="A50">
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C50" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E50" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F50" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ50">
         <v>200000</v>
@@ -3966,33 +3977,33 @@
         <v>30000</v>
       </c>
       <c r="AU50" t="s">
-        <v>338</v>
+        <v>340</v>
+      </c>
+      <c r="BF50">
+        <v>1</v>
       </c>
       <c r="BG50">
-        <v>1</v>
-      </c>
-      <c r="BH50">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:72">
+    <row r="51" spans="1:71">
       <c r="A51">
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D51" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E51" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F51" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AQ51">
         <v>500000</v>
@@ -4007,33 +4018,33 @@
         <v>125000</v>
       </c>
       <c r="AU51" t="s">
-        <v>343</v>
+        <v>345</v>
+      </c>
+      <c r="BF51">
+        <v>2</v>
       </c>
       <c r="BG51">
-        <v>2</v>
-      </c>
-      <c r="BH51">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:72">
+    <row r="52" spans="1:71">
       <c r="A52">
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D52" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F52" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ52">
         <v>2500</v>
@@ -4048,33 +4059,33 @@
         <v>150</v>
       </c>
       <c r="AU52" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI52" t="s">
-        <v>357</v>
-      </c>
-      <c r="BJ52">
+        <v>89</v>
+      </c>
+      <c r="BH52" t="s">
+        <v>359</v>
+      </c>
+      <c r="BI52">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:72">
+    <row r="53" spans="1:71">
       <c r="A53">
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D53" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ53">
         <v>5000</v>
@@ -4089,63 +4100,63 @@
         <v>200</v>
       </c>
       <c r="AU53" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI53" t="s">
-        <v>362</v>
-      </c>
-      <c r="BJ53">
+        <v>98</v>
+      </c>
+      <c r="BH53" t="s">
+        <v>364</v>
+      </c>
+      <c r="BI53">
         <v>1</v>
       </c>
+      <c r="BJ53" t="s">
+        <v>365</v>
+      </c>
       <c r="BK53" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="BL53" t="s">
-        <v>364</v>
-      </c>
-      <c r="BM53" t="s">
+        <v>367</v>
+      </c>
+      <c r="BM53">
+        <v>15</v>
+      </c>
+      <c r="BN53">
+        <v>1</v>
+      </c>
+      <c r="BO53" t="s">
         <v>365</v>
       </c>
-      <c r="BN53">
-        <v>15</v>
-      </c>
-      <c r="BO53">
-        <v>1</v>
-      </c>
       <c r="BP53" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="BQ53" t="s">
-        <v>366</v>
-      </c>
-      <c r="BR53" t="s">
-        <v>367</v>
+        <v>369</v>
+      </c>
+      <c r="BR53">
+        <v>20</v>
       </c>
       <c r="BS53">
-        <v>20</v>
-      </c>
-      <c r="BT53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:72">
+    <row r="54" spans="1:71">
       <c r="A54">
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C54" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E54" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F54" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AQ54">
         <v>5000</v>
@@ -4160,33 +4171,33 @@
         <v>500</v>
       </c>
       <c r="AU54" t="s">
-        <v>187</v>
-      </c>
-      <c r="BI54" t="s">
-        <v>372</v>
-      </c>
-      <c r="BJ54">
+        <v>189</v>
+      </c>
+      <c r="BH54" t="s">
+        <v>374</v>
+      </c>
+      <c r="BI54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:72">
+    <row r="55" spans="1:71">
       <c r="A55">
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D55" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E55" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F55" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AQ55">
         <v>2000</v>
@@ -4201,33 +4212,33 @@
         <v>175</v>
       </c>
       <c r="AU55" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI55" t="s">
-        <v>362</v>
-      </c>
-      <c r="BJ55">
+        <v>105</v>
+      </c>
+      <c r="BH55" t="s">
+        <v>364</v>
+      </c>
+      <c r="BI55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:72">
+    <row r="56" spans="1:71">
       <c r="A56">
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D56" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E56" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F56" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ56">
         <v>5000</v>
@@ -4242,42 +4253,42 @@
         <v>1000</v>
       </c>
       <c r="AU56" t="s">
-        <v>368</v>
+        <v>370</v>
+      </c>
+      <c r="BJ56" t="s">
+        <v>383</v>
       </c>
       <c r="BK56" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="BL56" t="s">
-        <v>382</v>
-      </c>
-      <c r="BM56" t="s">
-        <v>383</v>
+        <v>385</v>
+      </c>
+      <c r="BM56">
+        <v>25</v>
       </c>
       <c r="BN56">
-        <v>25</v>
-      </c>
-      <c r="BO56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:72">
+    <row r="57" spans="1:71">
       <c r="A57">
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C57" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D57" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E57" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F57" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AQ57">
         <v>5000</v>
@@ -4292,30 +4303,30 @@
         <v>350</v>
       </c>
       <c r="AU57" t="s">
-        <v>251</v>
-      </c>
-      <c r="BC57">
+        <v>253</v>
+      </c>
+      <c r="BB57">
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:72">
+    <row r="58" spans="1:71">
       <c r="A58">
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C58" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D58" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E58" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F58" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AQ58">
         <v>10000</v>
@@ -4330,12 +4341,12 @@
         <v>1000</v>
       </c>
       <c r="AU58" t="s">
-        <v>176</v>
-      </c>
-      <c r="BI58" t="s">
-        <v>392</v>
-      </c>
-      <c r="BJ58">
+        <v>178</v>
+      </c>
+      <c r="BH58" t="s">
+        <v>394</v>
+      </c>
+      <c r="BI58">
         <v>1</v>
       </c>
     </row>
